--- a/02_加值成品/九下/九下1-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下1-3_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下1-3 家庭用電與安全　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三下學期 九下1-3 家庭用電與安全　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>家庭電器採什麼連接？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>超載</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>熔斷斷電</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>過熱走火</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>並聯</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>獨立</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>電流過大自動斷電的是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>長期累積浪費能源與電費</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>前者防觸電漏電、後者防過流</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>水降低電阻使電流易通過人體</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>保險絲/無熔絲開關</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>保護</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>防止觸電的裝置是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>漏電斷路器</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>熔斷斷電</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>過熱走火</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>接地</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>保護</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>濕手觸碰電器？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>危險</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>接觸不良發熱</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>較省電</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>節約用電</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>易觸電</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>插座插太多電器會？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>過熱走火</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>熔斷斷電</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>接觸不良發熱</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>超載</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>過熱</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>三孔插頭多一孔用於？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>危險</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>超載</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>超載跳電</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>接地</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>安全</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>隨手關燈是為了？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>並聯</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>節約用電</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>接地</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>危險</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>節能</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>保險絲的作用是？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>危險</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>超載</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>接地</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>過流時斷電</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>保護</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>家庭電路各電器通常採？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>漏電斷路器</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>熔斷斷電</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>超載</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>並聯</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>並聯</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>電流過大時保險絲會？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>接地</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>超載</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>並聯</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>熔斷斷電</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>保護</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下1-3 家庭用電與安全　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三下學期 九下1-3 家庭用電與安全　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>家庭電器並聯的好處？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>總電流超過負載保護裝置斷電</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>保險絲/無熔絲開關</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>電流過載或短路</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>可獨立運作互不影響</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>並聯</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>保險絲為何要適當規格？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>使漏電電流經接地導走避免電擊</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>可獨立運作互不影響</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>太粗失去保護作用</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>並聯各電器獨立且電壓相同,一個壞不影響其他</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>規格</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>無熔絲開關跳電常因？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>使漏電電流經接地導走避免電擊</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>電器待機仍耗少量電</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>太粗失去保護作用</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>電流過載或短路</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>保護</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>接地能保護人是因為？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>避免超載選節能電器隨手關電</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>潮濕易導電增加觸電風險</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>漏電時電流導入地</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>電流過載或短路</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>導走</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>待機耗電指？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>電流過載或短路</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>總電流超過負載保護裝置斷電</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>電器待機仍耗少量電</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>太粗失去保護作用</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>節能</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>選能源標章電器是為了？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>較省電</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>過流時斷電</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>超載跳電</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>漏電斷路器</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>節能</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>延長線超載可能導致？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>過熱走火</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>漏電斷路器</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
           <t>危險</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="34" customHeight="1">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>過流時斷電</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>危險</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>插頭沒插緊可能造成？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>超載</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>接地</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>危險</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>接觸不良發熱</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>安全</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>三孔插座多的一孔作用是？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>危險</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>超載跳電</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>節約用電</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>接地</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>安全</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>同時使用多個大功率電器可能？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>接觸不良發熱</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>較省電</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>超載跳電</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>漏電斷路器</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>過載</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下1-3 家庭用電與安全　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三下學期 九下1-3 家庭用電與安全　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>為何家庭電路用並聯而非串聯？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>電流過大時熔斷切斷電流防過熱</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>潮濕易導電增加觸電風險</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>並聯各電器獨立且電壓相同,一個壞不影響其他</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>電流過載或短路</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>並聯</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>說明保險絲如何保護電路？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>太粗失去保護作用</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>電流過大時熔斷切斷電流防過熱</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>使漏電電流經接地導走避免電擊</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>電器待機仍耗少量電</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>保護</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>同時開很多大功率電器可能跳電原因？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>電器待機仍耗少量電</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>電流過載或短路</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>總電流超過負載保護裝置斷電</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>使漏電電流經接地導走避免電擊</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>過載</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>接地線在漏電時如何保護人？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>總電流超過負載保護裝置斷電</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>並聯各電器獨立且電壓相同,一個壞不影響其他</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>保險絲/無熔絲開關</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>使漏電電流經接地導走避免電擊</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>接地</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>如何規劃安全又節能的用電？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>水降低電阻使電流易通過人體</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>電流過載或短路</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>避免超載選節能電器隨手關電</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>總電流超過負載保護裝置斷電</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>綜合</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>濕手觸電為何更危險？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>水降低電阻使電流易通過人體</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>電器待機仍耗少量電</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>並聯各電器獨立且電壓相同,一個壞不影響其他</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>總電流超過負載保護裝置斷電</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>導電</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>漏電斷路器與保險絲功能差異？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>電器待機仍耗少量電</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>並聯各電器獨立且電壓相同,一個壞不影響其他</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>前者防觸電漏電、後者防過流</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>潮濕易導電增加觸電風險</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>區別</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>待機電力累積影響為何？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>電流過載或短路</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>電器待機仍耗少量電</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>長期累積浪費能源與電費</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>可獨立運作互不影響</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>節能</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何家庭用並聯使各電器獨立？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>電壓相同一個故障不影響其他</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>水降低電阻使電流易通過人體</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>電器待機仍耗少量電</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>使漏電電流經接地導走避免電擊</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>並聯</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>為何浴室用電要特別小心？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>電器待機仍耗少量電</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>漏電時電流導入地</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>保險絲/無熔絲開關</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>潮濕易導電增加觸電風險</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>安全</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九下/九下1-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下1-3_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>獨立</t>
+          <t>獨立：家裡的電器都是並聯連接，這樣每個電器才能獨立開關，互不影響</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>保護</t>
+          <t>保護：當電流超過安全範圍時，保險絲或無熔絲開關會自動切斷電路，避免危險</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>保護</t>
+          <t>保護：漏電斷路器會偵測到電流異常外洩，立刻切斷電源，防止人被電到</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>易觸電</t>
+          <t>易觸電：水會讓身體變得更容易導電，濕手碰電器容易發生觸電危險</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>過熱</t>
+          <t>過熱：一個插座接太多電器會讓電流過大，造成電線過熱甚至有走火的風險</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>安全</t>
+          <t>安全：三孔插頭多出來的那一孔是接地線，能在漏電時把電流導入大地保護人</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>節能</t>
+          <t>節能：不用電燈時隨手關掉，可以減少不必要的電能浪費，達到節約用電</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>保護</t>
+          <t>保護：保險絲在電流過大時會自己熔斷，切斷電路以保護家中電器與電線</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>並聯</t>
+          <t>並聯：家中電器大多以並聯方式連接，這樣才能各自獨立開關使用</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>保護</t>
+          <t>保護：保險絲在電流過大時會自動熔斷，切斷電路以保護電器與電線</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>並聯</t>
+          <t>並聯：並聯電路中每個電器各自獨立，關掉一個不會影響其他電器繼續使用</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>規格</t>
+          <t>規格：保險絲若選得太粗，電流過大時不容易熔斷，就失去了保護電路的作用</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>保護</t>
+          <t>保護：當電路裡的電流超過負荷或發生短路時，無熔絲開關就會跳脫斷電</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>導走</t>
+          <t>導走：接地線能讓漏出的電流優先流入大地，而不會經過人體造成觸電</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>節能</t>
+          <t>節能：電器即使關機沒使用，只要插頭還插著，仍會持續消耗少量電力</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>節能</t>
+          <t>節能：貼有能源標章的電器通常耗電效率較好，能達到省電的效果</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>危險</t>
+          <t>危險：延長線一次插太多電器會讓電流過大，電線過熱嚴重時可能引發火災</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>安全</t>
+          <t>安全：插頭沒有確實插緊會造成接觸不良，接點處容易發熱甚至冒出火花</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>安全</t>
+          <t>安全：三孔插座多出來的那一孔是接地線，能在漏電時把電流導入大地保護人</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>過載</t>
+          <t>過載：多個高功率電器一起使用會讓電流超過負荷，導致保護裝置跳電</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>並聯</t>
+          <t>並聯：並聯讓每個電器分到相同電壓且能獨立開關，一個電器故障也不影響其他電器運作</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>保護</t>
+          <t>保護：保險絲內部的金屬線在電流過大時會因發熱而熔斷，及時切斷電路避免過熱起火</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>過載</t>
+          <t>過載：多個大功率電器同時使用會讓總電流超過電路能負荷的範圍，保護裝置便會自動跳脫</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>接地</t>
+          <t>接地：接地線提供電流另一條容易通過的路徑，讓漏電的電流流入大地而不流經人體</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>綜合</t>
+          <t>綜合：不讓插座超載、選用省電標章電器，並養成隨手關燈關電源的習慣，就能兼顧安全與節能</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>導電</t>
+          <t>導電：水分會降低人體的電阻，讓電流更容易通過身體，因此濕手觸電特別危險</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>區別</t>
+          <t>區別：漏電斷路器主要偵測漏電以防止觸電，保險絲則是在電流過大時熔斷以防止過熱</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>節能</t>
+          <t>節能：許多電器待機時持續耗電，長期累積下來會浪費不少能源，也讓電費增加</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>並聯</t>
+          <t>並聯：並聯電路中每個電器分到相同電壓，其中一個故障也不會影響其他電器繼續運作</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>安全</t>
+          <t>安全：浴室環境潮濕，水分會降低人體電阻，使用電器時更容易發生觸電意外</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/九下/九下1-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下1-3_三種難度測驗卷.xlsx
@@ -723,17 +723,17 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>過熱走火</t>
+          <t>過流時斷電</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>熔斷斷電</t>
+          <t>漏電斷路器</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>接觸不良發熱</t>
+          <t>接地</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>接觸不良發熱</t>
+          <t>節約用電</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>較省電</t>
+          <t>過熱走火</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
